--- a/output/pdf_financials_xlsx/NTE.xlsx
+++ b/output/pdf_financials_xlsx/NTE.xlsx
@@ -5974,19 +5974,19 @@
         <v>0</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.054137</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.16421</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.125538</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.444085</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.416255</v>
       </c>
     </row>
     <row r="93">
@@ -10468,7 +10468,11 @@
           <t>Share-based payment reserve 16(c)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -13900,7 +13904,11 @@
           <t>Share-based payment reserve 15(c)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -15990,7 +15998,11 @@
           <t>Share-based payment reserve 12(c)</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NTE.xlsx
+++ b/output/pdf_financials_xlsx/NTE.xlsx
@@ -1114,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.008111</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         <v>-0.801961</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.7448</v>
+        <v>-0.752911</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-3.047897</v>
@@ -2311,7 +2311,7 @@
         <v>-0.801961</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.7448</v>
+        <v>-0.752911</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-3.047897</v>
@@ -2380,7 +2380,7 @@
         <v>-354.3216531101853</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-215.2818926770049</v>
+        <v>-217.6263494862197</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-177.8818504773149</v>
@@ -2621,22 +2621,22 @@
         <v>1.182454</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.685731</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.78873</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.708287</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.275164</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>3.016447</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>3.870289</v>
       </c>
     </row>
     <row r="35">
@@ -2731,22 +2731,22 @@
         <v>1.182454</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.685731</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.78873</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.708287</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.275164</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>3.016447</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>3.870289</v>
       </c>
     </row>
     <row r="37">
@@ -3391,22 +3391,22 @@
         <v>5.12697</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.708643</v>
+        <v>2.022912</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>4.455673</v>
+        <v>1.666943</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>5.174013</v>
+        <v>4.465726</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>6.055523</v>
+        <v>3.780359</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>4.963562</v>
+        <v>1.947115</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>7.571065</v>
+        <v>3.700776</v>
       </c>
     </row>
     <row r="49">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -29810,7 +29810,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E230" s="5" t="n">
@@ -56268,7 +56268,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">

--- a/output/pdf_financials_xlsx/NTE.xlsx
+++ b/output/pdf_financials_xlsx/NTE.xlsx
@@ -1054,10 +1054,10 @@
         <v>-0.518548</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.7857150000000001</v>
+        <v>0.052675</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2.187601</v>
+        <v>0.219105</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>8.110173</v>
@@ -1399,7 +1399,7 @@
         <v>-1.063509</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.050709</v>
+        <v>-0.103384</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0.118296</v>
@@ -1468,7 +1468,7 @@
         <v>-0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.052675</v>
+        <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0.009183999999999999</v>
@@ -2182,7 +2182,7 @@
         <v>-1.063509</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.050709</v>
+        <v>-0.103384</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>0.118296</v>
@@ -2320,7 +2320,7 @@
         <v>-1.063509</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.050709</v>
+        <v>-0.103384</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0.118296</v>
@@ -2389,7 +2389,7 @@
         <v>-3568.462906418817</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-3.515555130343631</v>
+        <v>-7.16740916988002</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>5.407567467742061</v>
@@ -2458,7 +2458,7 @@
         <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-103.8770238024808</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>7.763576114154325</v>
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.003989</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -7033,7 +7033,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.016289</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -38064,7 +38064,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -41638,7 +41642,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -51256,7 +51264,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
